--- a/InputData/elec/RACP/RPS Alternative Compliance Payment.xlsx
+++ b/InputData/elec/RACP/RPS Alternative Compliance Payment.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RACP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwlee_NG\Dropbox\NEXT Group\90. 개인 폴더\이지우\단기대응\202501 EPS 수요전망\V3\elec\RACP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F855F-5615-4B6F-8C76-6AC2301E3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E91BCA-742F-409E-9458-1DE3BA4F8D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{987F1A2C-D0FF-46D7-8396-B08F06D764BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{987F1A2C-D0FF-46D7-8396-B08F06D764BF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RACP-BRACP" sheetId="2" r:id="rId2"/>
-    <sheet name="RACP-RACP" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="RACP-BRACP" sheetId="2" r:id="rId3"/>
+    <sheet name="RACP-RACP" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>(to be updated).</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
@@ -52,36 +50,60 @@
     <t>Cost Cap</t>
   </si>
   <si>
+    <t>2023 dollars per 2012 dollar</t>
+  </si>
+  <si>
+    <t>BRACP BAU RPS Alternative Compliance Payment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.knrec.or.kr/biz/faq/faq_list02.do?depth_1=A010000&amp;depth_2=A011300</t>
+  </si>
+  <si>
     <t>RACP RPS Alternative Compliance Payment</t>
-  </si>
-  <si>
-    <t>This variable is input using the currency unit specified in web-app/OCCF, not 2012 USD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is because it is a control variable visible in the web app, so users will interact with </t>
-  </si>
-  <si>
-    <t>this lever in output currency units.</t>
-  </si>
-  <si>
-    <t>2023 dollars per 2012 dollar</t>
-  </si>
-  <si>
-    <t>BRACP BAU RPS Alternative Compliance Payment</t>
-  </si>
-  <si>
-    <t>For now, we put in a cost cap of $180/MWh.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RPS Alternative Compliance Payment standard in Korea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For shortages in Korea, suppliers should pay 1.5 times the average trading price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.mal-eum.com/rec/trend</t>
+  </si>
+  <si>
+    <t>REC average price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>price (KRW/REC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>price (USD/REC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exchange rate from 2017 to 2022</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>price * 1.5 (USD/REC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -89,8 +111,24 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -114,12 +152,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -135,7 +174,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -431,112 +470,448 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF84CE-31BD-44F2-91E9-58D4BA5F9B1E}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>0.75350342301658668</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18">
+        <v>2018</v>
+      </c>
+      <c r="C18">
+        <v>2019</v>
+      </c>
+      <c r="D18">
+        <v>2020</v>
+      </c>
+      <c r="E18">
+        <v>2021</v>
+      </c>
+      <c r="F18">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1150.4000000000001</v>
+      </c>
+      <c r="B19">
+        <v>1120.3499999999999</v>
+      </c>
+      <c r="C19">
+        <v>1186.92</v>
+      </c>
+      <c r="D19">
+        <v>1200.54</v>
+      </c>
+      <c r="E19">
+        <v>1165.0999999999999</v>
+      </c>
+      <c r="F19">
+        <v>1316.31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98D53A58-81B0-46BB-9D68-505A335381CB}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>2017</v>
+      </c>
+      <c r="C1">
+        <v>2018</v>
+      </c>
+      <c r="D1">
+        <v>2019</v>
+      </c>
+      <c r="E1">
+        <v>2020</v>
+      </c>
+      <c r="F1">
+        <v>2021</v>
+      </c>
+      <c r="G1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>123993</v>
+      </c>
+      <c r="C2">
+        <v>98028</v>
+      </c>
+      <c r="D2">
+        <v>62881</v>
+      </c>
+      <c r="E2">
+        <v>42000</v>
+      </c>
+      <c r="F2">
+        <v>36523</v>
+      </c>
+      <c r="G2">
+        <v>56478</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <f>B2/About!A19</f>
+        <v>107.78251043115438</v>
+      </c>
+      <c r="C3">
+        <f>C2/About!B19</f>
+        <v>87.497656982193078</v>
+      </c>
+      <c r="D3">
+        <f>D2/About!C19</f>
+        <v>52.978296768105679</v>
+      </c>
+      <c r="E3">
+        <f>E2/About!D19</f>
+        <v>34.984257084312063</v>
+      </c>
+      <c r="F3">
+        <f>F2/About!E19</f>
+        <v>31.347523817698054</v>
+      </c>
+      <c r="G3">
+        <f>G2/About!F19</f>
+        <v>42.906306265241476</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <f>B3*1.5</f>
+        <v>161.67376564673157</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:G4" si="0">C3*1.5</f>
+        <v>131.24648547328962</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>79.467445152158518</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>52.476385626468094</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>47.021285726547077</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>64.35945939786221</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D31B00E-6F0F-4633-A44F-D318C1E48FE8}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>180*About!A12</f>
-        <v>135.63061614298562</v>
+        <f>AVERAGE(Sheet1!B4:G4)</f>
+        <v>89.374137837176178</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE709EEA-4000-4167-85C9-4FB98ADCDFFE}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>9999</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D42F2E86-81A0-43E8-8135-8F95F1D5F5E4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A2C1BB-1C27-4365-9B2A-BD9D38981149}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ED0CA83-8341-4199-AD9E-EBA7572AB3EB}"/>
 </file>